--- a/artfynd/A 10977-2026 artfynd.xlsx
+++ b/artfynd/A 10977-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,56 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>101073272</v>
+        <v>96116556</v>
       </c>
       <c r="B2" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93190</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221235</v>
+        <v>786</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Brandtaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Hydnellum auratile</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Britzelm.) Maas Geest.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kåski, vid gräns mellan skiften. , Mpd</t>
+          <t>Kåski, Lillström. Sydväst om gränsmarkering till nytt hygge. Nära branten., Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592711.5631421198</v>
+        <v>592718</v>
       </c>
       <c r="R2" t="n">
-        <v>6924221.681651484</v>
+        <v>6924157</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,22 +743,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-05-23</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>09:05</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-05-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>09:05</t>
+          <t>2021-09-14</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Strax sydöst om fyndplatsen. Såg ett tiotal svampar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,6 +762,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -793,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>101423269</v>
+        <v>92402199</v>
       </c>
       <c r="B3" t="n">
-        <v>96367</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -809,44 +792,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219874</v>
+        <v>1205</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lillström, Stöde. På platån ovanför hygget. , Mpd</t>
+          <t>Kåski, Lillström, Stöde, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592713.3651908028</v>
+        <v>592761</v>
       </c>
       <c r="R3" t="n">
-        <v>6924173.547166151</v>
+        <v>6924336</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -873,22 +851,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-06-05</t>
+          <t>2021-04-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-06-05</t>
+          <t>2021-04-14</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,52 +893,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>101423431</v>
+        <v>96093210</v>
       </c>
       <c r="B4" t="n">
-        <v>96232</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90662</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219795</v>
+        <v>1594</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Svartfjällig musseron</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Tricholoma atrosquamosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>Sacc.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lillström , Mpd</t>
+          <t>Kåski, Lillström. Sydväst om gränsmarkering till nytt hygge. Nära branten., Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592697.2029873932</v>
+        <v>592718</v>
       </c>
       <c r="R4" t="n">
-        <v>6924187.460701348</v>
+        <v>6924157</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -987,22 +959,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-06-05</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-06-05</t>
+          <t>2021-09-14</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,6 +998,1092 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>96859877</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hjärtbäcken, övre delen. Norra sidan ravin., Mpd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>592763</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6924344</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-10-27</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-10-27</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>115270197</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kvarnbäcken, Kåski. Södra sidan., Lillström, Stöde, Mpd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>592390</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6924642</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-03-19</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>101423431</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99017</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219795</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grönkulla</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Coeloglossum viride</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lillström , Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>592697</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6924187</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-06-05</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-06-05</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>101423269</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lillström, Stöde. På platån ovanför hygget. , Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>592713</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6924174</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-06-05</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-06-05</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>94128706</v>
+      </c>
+      <c r="B9" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kåski, Lillström, Stöde, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>592761</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6924336</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-06-08</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-06-08</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>101073272</v>
+      </c>
+      <c r="B10" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kåski, vid gräns mellan skiften. , Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>592712</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6924222</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-05-23</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-05-23</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>95724538</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kåski, Lillström. Vid djurstig söder om gammal skogslägda., Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>592736</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6924240</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-08-25</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-08-25</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>94128773</v>
+      </c>
+      <c r="B12" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kåski, Lillström, Stöde, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>592761</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6924336</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-06-08</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-06-08</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>93283770</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kåski, Lillström, Stöde, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>592774</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6924336</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2021-05-11</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2021-05-11</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>94128809</v>
+      </c>
+      <c r="B14" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kåski, Lillström, Stöde, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>592761</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6924336</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2021-06-08</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2021-06-08</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Maja Lundahl</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10977-2026 artfynd.xlsx
+++ b/artfynd/A 10977-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96116556</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92402199</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96093210</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1106,6 +1126,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96859877</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1221,6 +1246,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115270197</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1330,6 +1360,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101423431</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1447,6 +1482,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101423269</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1549,6 +1589,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94128706</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1662,6 +1707,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101073272</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1771,6 +1821,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95724538</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1873,6 +1928,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94128773</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1982,6 +2042,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93283770</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2084,8 +2149,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94128809</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>